--- a/data/trans_dic/P12_2_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P12_2_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que refirió mucha energía alguna vez o algunas veces</t>
+          <t>Población que refirió mucha energía alguna vez o algunas veces (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,39; 25,96</t>
+          <t>15,65; 25,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,27; 32,53</t>
+          <t>22,37; 33,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,36; 33,56</t>
+          <t>22,47; 33,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,3; 28,47</t>
+          <t>18,1; 27,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,14; 26,21</t>
+          <t>16,31; 26,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,0; 38,67</t>
+          <t>26,53; 37,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,43; 44,48</t>
+          <t>32,38; 44,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,06; 39,1</t>
+          <t>30,19; 39,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,11; 24,14</t>
+          <t>17,26; 24,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,23; 34,11</t>
+          <t>25,91; 33,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,97; 37,43</t>
+          <t>28,77; 37,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,11; 31,81</t>
+          <t>25,0; 32,04</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,9; 27,46</t>
+          <t>19,76; 27,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 13,4</t>
+          <t>7,2; 13,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,07; 16,11</t>
+          <t>10,25; 15,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 14,11</t>
+          <t>7,87; 14,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,26; 37,74</t>
+          <t>29,74; 37,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,79; 21,79</t>
+          <t>15,04; 21,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,87; 23,33</t>
+          <t>15,33; 22,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,78; 21,59</t>
+          <t>15,79; 21,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,85; 31,51</t>
+          <t>25,93; 31,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,7; 16,24</t>
+          <t>11,67; 16,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,53; 18,27</t>
+          <t>13,63; 18,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,51; 16,59</t>
+          <t>12,7; 16,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,22; 15,17</t>
+          <t>7,57; 15,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,42; 19,41</t>
+          <t>11,41; 19,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,2; 25,85</t>
+          <t>16,82; 25,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,0; 20,96</t>
+          <t>12,49; 19,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,64; 25,39</t>
+          <t>16,9; 25,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,84; 24,87</t>
+          <t>15,85; 25,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,99; 29,0</t>
+          <t>19,66; 29,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,02; 20,42</t>
+          <t>13,93; 20,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,4; 19,21</t>
+          <t>13,42; 19,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,8; 21,13</t>
+          <t>14,97; 20,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,4; 25,74</t>
+          <t>19,38; 26,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,19; 19,22</t>
+          <t>14,32; 19,09</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,46; 17,68</t>
+          <t>10,51; 17,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,72; 22,99</t>
+          <t>14,78; 22,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,52; 25,24</t>
+          <t>16,65; 25,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,92; 24,19</t>
+          <t>14,01; 24,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,54; 31,69</t>
+          <t>22,71; 31,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,04; 44,2</t>
+          <t>34,21; 43,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,54; 32,09</t>
+          <t>22,66; 32,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,43; 22,68</t>
+          <t>10,35; 22,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,79; 23,69</t>
+          <t>17,75; 23,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,92; 33,0</t>
+          <t>25,68; 32,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,95; 27,17</t>
+          <t>20,95; 27,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,82; 21,53</t>
+          <t>13,04; 21,46</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,27; 40,31</t>
+          <t>27,6; 40,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,38; 21,65</t>
+          <t>11,26; 21,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,68; 27,85</t>
+          <t>16,49; 27,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,91; 44,5</t>
+          <t>32,5; 45,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,57; 51,53</t>
+          <t>37,85; 52,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,59; 39,35</t>
+          <t>27,1; 40,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,77; 33,36</t>
+          <t>21,5; 33,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>46,58; 56,38</t>
+          <t>46,63; 56,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,45; 44,13</t>
+          <t>34,42; 43,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,27; 28,95</t>
+          <t>20,73; 28,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20,66; 28,93</t>
+          <t>20,56; 28,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,86; 49,56</t>
+          <t>41,82; 49,61</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,03; 16,44</t>
+          <t>8,96; 16,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,6; 19,33</t>
+          <t>10,65; 19,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,17; 16,81</t>
+          <t>9,25; 17,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,1; 20,64</t>
+          <t>12,77; 20,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,65; 33,34</t>
+          <t>22,75; 33,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,03; 22,02</t>
+          <t>13,43; 22,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,95; 24,03</t>
+          <t>13,89; 23,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,74; 19,33</t>
+          <t>12,39; 19,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,73; 23,66</t>
+          <t>17,06; 23,63</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,14; 19,8</t>
+          <t>12,91; 19,28</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,65; 19,04</t>
+          <t>12,59; 18,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,89; 18,76</t>
+          <t>13,93; 18,72</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,99; 12,81</t>
+          <t>8,09; 12,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,98; 24,14</t>
+          <t>17,37; 24,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,73; 19,67</t>
+          <t>13,76; 20,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,09; 23,43</t>
+          <t>16,24; 23,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,52; 26,49</t>
+          <t>19,66; 26,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,51; 29,67</t>
+          <t>22,54; 29,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,8; 27,7</t>
+          <t>21,08; 27,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,75; 27,32</t>
+          <t>9,92; 27,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,63; 18,92</t>
+          <t>14,67; 18,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,95; 25,77</t>
+          <t>21,05; 26,11</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,25; 22,83</t>
+          <t>18,32; 22,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,42; 23,99</t>
+          <t>12,59; 24,03</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,31; 33,03</t>
+          <t>26,14; 33,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,94; 20,6</t>
+          <t>14,71; 20,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,14</t>
+          <t>5,65; 9,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,27; 11,58</t>
+          <t>3,54; 11,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,21; 41,45</t>
+          <t>33,99; 40,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,86; 27,03</t>
+          <t>20,99; 27,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,16; 16,33</t>
+          <t>11,25; 16,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,91; 20,99</t>
+          <t>16,13; 21,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,06; 36,13</t>
+          <t>30,98; 36,15</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18,82; 22,95</t>
+          <t>18,73; 22,99</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,06; 12,23</t>
+          <t>9,07; 12,23</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,47; 15,15</t>
+          <t>7,93; 15,4</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,28; 21,04</t>
+          <t>18,2; 21,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,01; 18,69</t>
+          <t>15,92; 18,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14,49; 17,0</t>
+          <t>14,5; 16,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,14; 17,46</t>
+          <t>12,16; 17,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,97; 31,19</t>
+          <t>28,09; 31,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,99; 26,97</t>
+          <t>24,05; 27,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,88; 23,83</t>
+          <t>20,88; 23,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17,3; 23,51</t>
+          <t>17,9; 23,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23,52; 25,71</t>
+          <t>23,6; 25,71</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20,45; 22,52</t>
+          <t>20,49; 22,5</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,06; 20,08</t>
+          <t>18,1; 19,97</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,43; 20,26</t>
+          <t>16,5; 20,24</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que refirió mucha energía alguna vez o algunas veces</t>
+          <t>Población que refirió mucha energía alguna vez o algunas veces (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42004; 70865</t>
+          <t>42738; 70567</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>65630; 95869</t>
+          <t>65920; 97902</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65465; 98249</t>
+          <t>65776; 96883</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56985; 88670</t>
+          <t>56380; 87186</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42103; 68364</t>
+          <t>42543; 68029</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77570; 111078</t>
+          <t>76220; 108382</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93636; 128401</t>
+          <t>93494; 127918</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>87074; 113239</t>
+          <t>87432; 115452</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>91340; 128852</t>
+          <t>92147; 128909</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>152629; 198489</t>
+          <t>150801; 196846</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>168471; 217623</t>
+          <t>167303; 215541</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>150932; 191220</t>
+          <t>150293; 192595</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>98100; 135398</t>
+          <t>97411; 136196</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36656; 67729</t>
+          <t>36384; 66048</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50518; 80757</t>
+          <t>51384; 80135</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42001; 73158</t>
+          <t>40802; 74348</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>147480; 190178</t>
+          <t>149899; 190343</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76882; 113263</t>
+          <t>78181; 111593</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82660; 121530</t>
+          <t>79873; 118053</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81264; 111157</t>
+          <t>81335; 111277</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>257702; 314190</t>
+          <t>258530; 312849</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>119933; 166531</t>
+          <t>119626; 167266</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>138284; 186772</t>
+          <t>139350; 189218</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>129276; 171402</t>
+          <t>131222; 174917</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26214; 48374</t>
+          <t>24141; 48852</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37011; 62902</t>
+          <t>36973; 64076</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54808; 82341</t>
+          <t>53575; 80246</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40973; 66035</t>
+          <t>39350; 62679</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55829; 85165</t>
+          <t>56694; 84747</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54019; 84805</t>
+          <t>54063; 85676</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66853; 96967</t>
+          <t>65737; 98330</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>48648; 70850</t>
+          <t>48321; 70959</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>87674; 125676</t>
+          <t>87805; 126080</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>98406; 140502</t>
+          <t>99590; 138464</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>126645; 168058</t>
+          <t>126533; 169822</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>93935; 127224</t>
+          <t>94837; 126404</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37506; 63413</t>
+          <t>37682; 63919</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54906; 85774</t>
+          <t>55129; 85418</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61107; 93365</t>
+          <t>61602; 94026</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43503; 75608</t>
+          <t>43789; 75459</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83743; 117717</t>
+          <t>84341; 117499</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>132390; 171899</t>
+          <t>133065; 170185</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87102; 124004</t>
+          <t>87543; 124617</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49516; 107675</t>
+          <t>49111; 107335</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>129925; 172968</t>
+          <t>129605; 171711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>197493; 251463</t>
+          <t>195677; 247576</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>158431; 205488</t>
+          <t>158477; 207397</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>100964; 169493</t>
+          <t>102675; 168952</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>55443; 81950</t>
+          <t>56119; 83280</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24204; 46032</t>
+          <t>23949; 45849</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35235; 58827</t>
+          <t>34831; 58887</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58824; 79536</t>
+          <t>58097; 80492</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>78016; 107020</t>
+          <t>78594; 108130</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58390; 86416</t>
+          <t>59499; 88672</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47578; 72919</t>
+          <t>47003; 73935</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>96990; 117400</t>
+          <t>97092; 118169</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>141583; 181376</t>
+          <t>141449; 179296</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>87599; 125104</t>
+          <t>89616; 124663</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88813; 124328</t>
+          <t>88382; 123023</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>161975; 191768</t>
+          <t>161834; 191982</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24456; 44510</t>
+          <t>24264; 45692</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29055; 52955</t>
+          <t>29191; 54406</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24117; 44232</t>
+          <t>24336; 45316</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35323; 55660</t>
+          <t>34443; 55602</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>62992; 92739</t>
+          <t>63275; 92625</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36376; 61452</t>
+          <t>37476; 62455</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38112; 65617</t>
+          <t>37948; 64543</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>32752; 49677</t>
+          <t>31847; 49116</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>91842; 129872</t>
+          <t>93630; 129743</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72675; 109504</t>
+          <t>71384; 106621</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67818; 102105</t>
+          <t>67526; 100919</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>73156; 98795</t>
+          <t>73347; 98580</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>49158; 78801</t>
+          <t>49750; 79434</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>112512; 160017</t>
+          <t>115154; 159117</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>90174; 129151</t>
+          <t>90364; 133196</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100465; 146270</t>
+          <t>101383; 144849</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>124590; 169062</t>
+          <t>125465; 166437</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>155959; 205593</t>
+          <t>156154; 204693</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>143556; 191126</t>
+          <t>145443; 190800</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>91310; 231990</t>
+          <t>84231; 235373</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>183347; 237128</t>
+          <t>183910; 235966</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>284059; 349332</t>
+          <t>285341; 353902</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>245770; 307440</t>
+          <t>246745; 307769</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>182955; 353437</t>
+          <t>185483; 354107</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>195723; 245704</t>
+          <t>194433; 245916</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>116084; 160042</t>
+          <t>114321; 157266</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>43333; 70978</t>
+          <t>43875; 72552</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30366; 107510</t>
+          <t>32908; 107659</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>268031; 324728</t>
+          <t>266324; 320318</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>171658; 222365</t>
+          <t>172668; 222623</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>92191; 134898</t>
+          <t>92947; 135176</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>114215; 150679</t>
+          <t>115806; 151271</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>474393; 551748</t>
+          <t>473095; 552163</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>301038; 367237</t>
+          <t>299608; 367825</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>145179; 195999</t>
+          <t>145305; 196022</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>122940; 249423</t>
+          <t>130506; 253558</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1331981</t>
+          <t>1331980</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>598980; 689419</t>
+          <t>596418; 688815</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>548288; 639920</t>
+          <t>545171; 638447</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>491393; 576178</t>
+          <t>491489; 575962</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>419986; 604028</t>
+          <t>420698; 606902</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>945138; 1053966</t>
+          <t>949121; 1056738</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>852035; 957667</t>
+          <t>854156; 962705</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>738735; 843103</t>
+          <t>738815; 839917</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>632844; 859981</t>
+          <t>654772; 858035</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1565663; 1710947</t>
+          <t>1570526; 1711115</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1426614; 1570610</t>
+          <t>1429118; 1569444</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1251189; 1390966</t>
+          <t>1254017; 1383754</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1169148; 1441937</t>
+          <t>1174208; 1440269</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P12_2_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P12_2_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,65; 25,85</t>
+          <t>15,28; 25,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,37; 33,22</t>
+          <t>22,17; 32,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,47; 33,09</t>
+          <t>22,66; 33,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,1; 27,99</t>
+          <t>20,77; 29,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,31; 26,08</t>
+          <t>16,3; 26,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,53; 37,73</t>
+          <t>26,01; 37,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,38; 44,31</t>
+          <t>32,67; 43,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,19; 39,86</t>
+          <t>31,27; 40,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,26; 24,15</t>
+          <t>16,92; 24,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,91; 33,82</t>
+          <t>25,84; 33,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,77; 37,07</t>
+          <t>29,35; 37,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,0; 32,04</t>
+          <t>27,21; 33,76</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,76; 27,62</t>
+          <t>19,78; 27,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 13,07</t>
+          <t>7,28; 12,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,25; 15,98</t>
+          <t>10,13; 16,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 14,34</t>
+          <t>8,07; 14,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,74; 37,77</t>
+          <t>29,64; 37,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,04; 21,47</t>
+          <t>14,84; 21,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,33; 22,66</t>
+          <t>15,66; 22,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,79; 21,61</t>
+          <t>15,71; 21,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,93; 31,38</t>
+          <t>25,84; 31,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,67; 16,31</t>
+          <t>11,89; 16,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,63; 18,51</t>
+          <t>13,82; 18,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,7; 16,93</t>
+          <t>12,79; 17,03</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,57; 15,32</t>
+          <t>7,99; 15,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,41; 19,77</t>
+          <t>11,48; 19,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,82; 25,19</t>
+          <t>16,6; 25,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,49; 19,89</t>
+          <t>12,64; 20,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,9; 25,27</t>
+          <t>16,72; 25,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,85; 25,12</t>
+          <t>15,93; 24,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,66; 29,41</t>
+          <t>19,89; 29,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,93; 20,45</t>
+          <t>14,09; 20,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,42; 19,27</t>
+          <t>13,62; 19,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,97; 20,82</t>
+          <t>14,82; 21,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,38; 26,01</t>
+          <t>19,3; 26,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,32; 19,09</t>
+          <t>14,21; 18,92</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,51; 17,82</t>
+          <t>10,29; 17,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,78; 22,9</t>
+          <t>15,02; 23,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,65; 25,41</t>
+          <t>16,5; 25,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,01; 24,14</t>
+          <t>13,24; 23,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,71; 31,63</t>
+          <t>22,55; 31,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,21; 43,75</t>
+          <t>34,18; 44,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,66; 32,25</t>
+          <t>22,67; 32,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,35; 22,61</t>
+          <t>18,0; 25,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,75; 23,52</t>
+          <t>17,71; 23,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,68; 32,49</t>
+          <t>25,84; 32,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,95; 27,42</t>
+          <t>20,96; 27,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,04; 21,46</t>
+          <t>16,8; 22,79</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>44,16%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,6; 40,96</t>
+          <t>27,49; 41,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,26; 21,56</t>
+          <t>11,2; 21,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,49; 27,88</t>
+          <t>16,27; 27,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,5; 45,03</t>
+          <t>31,33; 42,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,85; 52,07</t>
+          <t>37,87; 51,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,1; 40,38</t>
+          <t>26,59; 39,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,5; 33,82</t>
+          <t>21,41; 33,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>46,63; 56,75</t>
+          <t>46,01; 55,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,42; 43,63</t>
+          <t>34,61; 44,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,73; 28,84</t>
+          <t>20,65; 28,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20,56; 28,62</t>
+          <t>20,69; 28,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,82; 49,61</t>
+          <t>40,02; 48,0</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,96; 16,87</t>
+          <t>8,91; 16,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,65; 19,86</t>
+          <t>10,66; 19,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,25; 17,22</t>
+          <t>9,23; 16,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,77; 20,62</t>
+          <t>12,86; 19,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,75; 33,3</t>
+          <t>22,36; 33,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,43; 22,38</t>
+          <t>13,23; 22,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,89; 23,63</t>
+          <t>13,46; 23,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,39; 19,11</t>
+          <t>12,86; 19,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,06; 23,63</t>
+          <t>16,92; 23,8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,91; 19,28</t>
+          <t>13,38; 19,59</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,59; 18,82</t>
+          <t>12,51; 19,06</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,93; 18,72</t>
+          <t>13,68; 18,77</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,09; 12,92</t>
+          <t>8,07; 12,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,37; 24,01</t>
+          <t>16,82; 23,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,76; 20,29</t>
+          <t>14,09; 19,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,24; 23,2</t>
+          <t>16,52; 23,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,66; 26,08</t>
+          <t>19,9; 26,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,54; 29,54</t>
+          <t>22,58; 29,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,08; 27,65</t>
+          <t>21,01; 27,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,92; 27,71</t>
+          <t>24,09; 29,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,67; 18,83</t>
+          <t>14,75; 18,85</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,05; 26,11</t>
+          <t>20,87; 25,74</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,32; 22,86</t>
+          <t>18,33; 22,75</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,59; 24,03</t>
+          <t>21,25; 25,8</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,14; 33,06</t>
+          <t>26,08; 32,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,71; 20,24</t>
+          <t>14,67; 20,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,34</t>
+          <t>5,66; 9,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,54; 11,59</t>
+          <t>8,43; 12,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,99; 40,88</t>
+          <t>34,0; 40,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,99; 27,06</t>
+          <t>20,71; 26,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,25; 16,36</t>
+          <t>11,28; 16,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,13; 21,08</t>
+          <t>15,48; 20,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,98; 36,15</t>
+          <t>31,1; 36,04</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18,73; 22,99</t>
+          <t>18,58; 22,88</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,07; 12,23</t>
+          <t>9,07; 12,3</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,93; 15,4</t>
+          <t>12,75; 15,71</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,2; 21,02</t>
+          <t>18,06; 20,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,92; 18,65</t>
+          <t>15,99; 18,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14,5; 16,99</t>
+          <t>14,51; 16,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,16; 17,55</t>
+          <t>15,64; 18,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>28,09; 31,27</t>
+          <t>28,22; 31,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,05; 27,11</t>
+          <t>24,02; 27,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,88; 23,74</t>
+          <t>20,79; 23,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17,9; 23,45</t>
+          <t>22,21; 24,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23,6; 25,71</t>
+          <t>23,63; 25,77</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20,49; 22,5</t>
+          <t>20,47; 22,53</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,1; 19,97</t>
+          <t>18,04; 20,07</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,5; 20,24</t>
+          <t>19,35; 21,16</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71432</t>
+          <t>79790</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>113014</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>171431</t>
+          <t>192804</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42738; 70567</t>
+          <t>41725; 68912</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>65920; 97902</t>
+          <t>65352; 97009</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65776; 96883</t>
+          <t>66338; 97120</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56380; 87186</t>
+          <t>66231; 95373</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42543; 68029</t>
+          <t>42510; 69861</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76220; 108382</t>
+          <t>74709; 108409</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93494; 127918</t>
+          <t>94325; 125996</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>87432; 115452</t>
+          <t>98833; 127247</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>92147; 128909</t>
+          <t>90302; 128824</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>150801; 196846</t>
+          <t>150356; 195939</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167303; 215541</t>
+          <t>170668; 215216</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>150293; 192595</t>
+          <t>172730; 214323</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55735</t>
+          <t>57955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>95115</t>
+          <t>101125</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>150850</t>
+          <t>159080</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97411; 136196</t>
+          <t>97532; 135814</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36384; 66048</t>
+          <t>36788; 65007</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51384; 80135</t>
+          <t>50777; 80414</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40802; 74348</t>
+          <t>42828; 76461</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>149899; 190343</t>
+          <t>149383; 189851</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78181; 111593</t>
+          <t>77135; 112854</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79873; 118053</t>
+          <t>81578; 117993</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81335; 111277</t>
+          <t>85866; 118371</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>258530; 312849</t>
+          <t>257643; 313541</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>119626; 167266</t>
+          <t>121863; 169049</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>139350; 189218</t>
+          <t>141331; 187757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>131222; 174917</t>
+          <t>137758; 183403</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50309</t>
+          <t>50138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59122</t>
+          <t>60079</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>109431</t>
+          <t>110216</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24141; 48852</t>
+          <t>25476; 48742</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36973; 64076</t>
+          <t>37214; 63832</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53575; 80246</t>
+          <t>52897; 81609</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39350; 62679</t>
+          <t>39814; 64168</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>56694; 84747</t>
+          <t>56074; 84590</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54063; 85676</t>
+          <t>54337; 83588</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65737; 98330</t>
+          <t>66512; 98506</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>48321; 70959</t>
+          <t>49936; 72579</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>87805; 126080</t>
+          <t>89132; 126853</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99590; 138464</t>
+          <t>98536; 140394</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>126533; 169822</t>
+          <t>126044; 169773</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>94837; 126404</t>
+          <t>95108; 126663</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57467</t>
+          <t>65712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>81406</t>
+          <t>89771</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>138873</t>
+          <t>155482</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37682; 63919</t>
+          <t>36913; 62189</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55129; 85418</t>
+          <t>56017; 86977</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61602; 94026</t>
+          <t>61029; 92887</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43789; 75459</t>
+          <t>49392; 86581</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84341; 117499</t>
+          <t>83752; 118738</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>133065; 170185</t>
+          <t>132947; 171128</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87543; 124617</t>
+          <t>87580; 124571</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49111; 107335</t>
+          <t>75755; 106884</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>129605; 171711</t>
+          <t>129303; 169950</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>195677; 247576</t>
+          <t>196860; 247087</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>158477; 207397</t>
+          <t>158527; 206878</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>102675; 168952</t>
+          <t>133422; 180970</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68775</t>
+          <t>76026</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>107513</t>
+          <t>114911</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>176288</t>
+          <t>190937</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>56119; 83280</t>
+          <t>55892; 83985</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23949; 45849</t>
+          <t>23823; 45128</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34831; 58887</t>
+          <t>34374; 57388</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58097; 80492</t>
+          <t>64426; 86741</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>78594; 108130</t>
+          <t>78636; 106628</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>59499; 88672</t>
+          <t>58392; 87685</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47003; 73935</t>
+          <t>46790; 73430</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>97092; 118169</t>
+          <t>104323; 125471</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>141449; 179296</t>
+          <t>142224; 181830</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89616; 124663</t>
+          <t>89254; 124393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88382; 123023</t>
+          <t>88912; 124031</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>161834; 191982</t>
+          <t>173037; 207562</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44746</t>
+          <t>43746</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>40577</t>
+          <t>41714</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>85323</t>
+          <t>85461</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24264; 45692</t>
+          <t>24140; 45308</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29191; 54406</t>
+          <t>29209; 52558</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24336; 45316</t>
+          <t>24288; 44052</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34443; 55602</t>
+          <t>34807; 54028</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>63275; 92625</t>
+          <t>62187; 92830</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37476; 62455</t>
+          <t>36925; 61752</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37948; 64543</t>
+          <t>36757; 64229</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>31847; 49116</t>
+          <t>33909; 50639</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>93630; 129743</t>
+          <t>92857; 130631</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71384; 106621</t>
+          <t>73977; 108322</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67526; 100919</t>
+          <t>67103; 102211</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>73347; 98580</t>
+          <t>73100; 100321</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123086</t>
+          <t>139677</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>171890</t>
+          <t>208833</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>294976</t>
+          <t>348509</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>49750; 79434</t>
+          <t>49611; 79510</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>115154; 159117</t>
+          <t>111486; 157896</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>90364; 133196</t>
+          <t>92479; 128760</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>101383; 144849</t>
+          <t>118873; 165603</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>125465; 166437</t>
+          <t>126985; 168652</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>156154; 204693</t>
+          <t>156477; 205864</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>145443; 190800</t>
+          <t>144986; 191638</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>84231; 235373</t>
+          <t>186019; 230645</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>183910; 235966</t>
+          <t>184893; 236279</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>285341; 353902</t>
+          <t>282988; 348992</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>246745; 307769</t>
+          <t>246832; 306397</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>185483; 354107</t>
+          <t>317043; 384813</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73440</t>
+          <t>83167</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>131369</t>
+          <t>147448</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>204809</t>
+          <t>230615</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>194433; 245916</t>
+          <t>194006; 244528</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>114321; 157266</t>
+          <t>113964; 157919</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>43875; 72552</t>
+          <t>43948; 72035</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>32908; 107659</t>
+          <t>67247; 100801</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>266324; 320318</t>
+          <t>266379; 319851</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>172668; 222623</t>
+          <t>170427; 220492</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>92947; 135176</t>
+          <t>93173; 132365</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>115806; 151271</t>
+          <t>128685; 167421</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>473095; 552163</t>
+          <t>475001; 550483</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>299608; 367825</t>
+          <t>297278; 365997</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>145305; 196022</t>
+          <t>145301; 197125</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>130506; 253558</t>
+          <t>207711; 255964</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>544990</t>
+          <t>596210</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>786991</t>
+          <t>876895</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1331980</t>
+          <t>1473105</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>596418; 688815</t>
+          <t>591793; 681939</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>545171; 638447</t>
+          <t>547437; 641713</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>491489; 575962</t>
+          <t>491833; 575631</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>420698; 606902</t>
+          <t>552243; 642562</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>949121; 1056738</t>
+          <t>953571; 1057287</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>854156; 962705</t>
+          <t>852908; 959982</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>738815; 839917</t>
+          <t>735629; 842539</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>654772; 858035</t>
+          <t>828645; 918372</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1570526; 1711115</t>
+          <t>1573002; 1715364</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1429118; 1569444</t>
+          <t>1427648; 1571345</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1254017; 1383754</t>
+          <t>1249836; 1390239</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1174208; 1440269</t>
+          <t>1405651; 1536612</t>
         </is>
       </c>
     </row>
